--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\TXR Academy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31B8C803-00A1-49E7-948B-EE9D61E49EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BAE8E7-F2EC-4985-969D-8D05724B32AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>12</v>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BAE8E7-F2EC-4985-969D-8D05724B32AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF535C-8301-474F-A0CB-864BFCD4BE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
   <si>
     <t>Sprint</t>
   </si>
@@ -163,9 +163,6 @@
     <t>US9</t>
   </si>
   <si>
-    <t>Procurement of load cell,gas sensor and shut-off valve</t>
-  </si>
-  <si>
     <t>Sprint 5</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
     <t>Interfacing load cell with processing platform for weight monitoring</t>
   </si>
   <si>
-    <t>Develop the logic for measuring the weight of the cylinder, leak classification,anomaly detection and prediction.Fix the conditions,limits and threshold for operation.</t>
-  </si>
-  <si>
     <t>US12</t>
   </si>
   <si>
@@ -197,6 +191,15 @@
   </si>
   <si>
     <t>Integration of modules and testing the behaviour</t>
+  </si>
+  <si>
+    <t>Read ADC values by interfacing MQ2,MQ4 and MQ7 gas sensor</t>
+  </si>
+  <si>
+    <t>Write the driver code and header files for reading data from MQ2,MQ4 and MQ7 gas sensor</t>
+  </si>
+  <si>
+    <t>Procurement of load cell,gas sensor, temp and humidity sensor</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1004"/>
+  <dimension ref="A1:Z1005"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -704,7 +707,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>10</v>
@@ -764,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -791,7 +794,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -805,11 +808,11 @@
         <v>41</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>3</v>
@@ -826,7 +829,7 @@
     </row>
     <row r="10" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
@@ -835,58 +838,53 @@
         <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="3"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3">
-        <v>7</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
@@ -900,25 +898,25 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
@@ -927,40 +925,53 @@
     </row>
     <row r="14" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+    <row r="15" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="3">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3">
+        <v>7</v>
+      </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -984,6 +995,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
@@ -995,9 +1007,9 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1017,6 +1029,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
@@ -1067,7 +1080,6 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
@@ -1078,6 +1090,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
@@ -1088,7 +1101,6 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
@@ -1112,20 +1124,20 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
@@ -1136,6 +1148,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
@@ -1166,7 +1179,6 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1177,6 +1189,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1187,7 +1200,6 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
@@ -1198,6 +1210,7 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
@@ -1209,48 +1222,57 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+    </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="6" t="s">
+    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C44" s="7"/>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2207,19 +2229,20 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F29 F31:F33" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F30 F32:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I18 I20:I29 I31:I39" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I19 I21:I30 I32:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E29 E31:E39" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$L$9:$L$10</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E30 E32:E40" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>$L$9:$L$11</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF535C-8301-474F-A0CB-864BFCD4BE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAD885F-9AD9-4090-B1EA-EED4400F5B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
   <si>
     <t>Sprint</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Quality Assurance</t>
   </si>
   <si>
-    <t>Name1</t>
-  </si>
-  <si>
     <t>Name2</t>
   </si>
   <si>
@@ -199,7 +196,34 @@
     <t>Write the driver code and header files for reading data from MQ2,MQ4 and MQ7 gas sensor</t>
   </si>
   <si>
-    <t>Procurement of load cell,gas sensor, temp and humidity sensor</t>
+    <t>Procurement of load cell with HX711 module,MQ2,MQ4,MQ7 gas sensors, DHT22</t>
+  </si>
+  <si>
+    <t>Write the .c and .h files for reading data from loadcell with HX711 module</t>
+  </si>
+  <si>
+    <t>Write the .c and .h files for reading data from DHT22 temp and humidity sensor</t>
+  </si>
+  <si>
+    <t>US14</t>
+  </si>
+  <si>
+    <t>Test the gas sensors using smoke or butane source to ensure that PPM concentration changes unlike the readings in clean air.</t>
+  </si>
+  <si>
+    <t>US15</t>
+  </si>
+  <si>
+    <t>US16</t>
+  </si>
+  <si>
+    <t>US17</t>
+  </si>
+  <si>
+    <t>US18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read load cell values with HX711 module using a known weight </t>
   </si>
 </sst>
 </file>
@@ -527,7 +551,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1005"/>
+  <dimension ref="A1:Z1009"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -591,16 +615,16 @@
     </row>
     <row r="2" spans="1:26" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
@@ -619,16 +643,16 @@
     </row>
     <row r="3" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3" t="s">
@@ -652,16 +676,16 @@
     </row>
     <row r="4" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
@@ -674,7 +698,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>14</v>
@@ -685,16 +709,16 @@
     </row>
     <row r="5" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
@@ -718,16 +742,16 @@
     </row>
     <row r="6" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
@@ -740,25 +764,25 @@
         <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -767,25 +791,25 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8" s="3">
         <v>3</v>
@@ -799,29 +823,25 @@
     </row>
     <row r="9" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="3">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3</v>
-      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -829,198 +849,261 @@
     </row>
     <row r="10" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="3">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
       <c r="I11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G12" s="3">
-        <v>7</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3</v>
+      </c>
       <c r="I12" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" s="3">
-        <v>7</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3</v>
+      </c>
       <c r="I13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="3">
-        <v>12</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>60</v>
+      </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" s="3">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3</v>
+      </c>
       <c r="I14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
+    <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>62</v>
+      </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" s="3">
-        <v>7</v>
-      </c>
-      <c r="H15" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3</v>
+      </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+    <row r="16" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="3">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="3">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
+        <v>7</v>
+      </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="I17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="3">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>5</v>
+      </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="3">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="3">
+        <v>7</v>
+      </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1032,6 +1115,7 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1040,8 +1124,10 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -1052,6 +1138,7 @@
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1060,6 +1147,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
@@ -1070,6 +1158,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
@@ -1090,7 +1179,6 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
@@ -1111,7 +1199,6 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
@@ -1122,7 +1209,6 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
@@ -1135,9 +1221,15 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
@@ -1159,6 +1251,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
@@ -1169,16 +1262,11 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1210,7 +1298,6 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
@@ -1231,64 +1318,102 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+    </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="7"/>
-    </row>
-    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
+      <c r="C48" s="7"/>
+    </row>
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
+    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C50" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C51" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
+    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C52" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2230,19 +2355,23 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F30 F32:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F36:F38 F2:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I19 I21:I30 I32:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I36:I44 I25:I34 I2:I23" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E30 E32:E40" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$L$9:$L$11</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E36:E44 E16:E34 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAD885F-9AD9-4090-B1EA-EED4400F5B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC321C-32C0-42DF-B630-59816D6F37E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,7 +923,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -974,7 +974,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC321C-32C0-42DF-B630-59816D6F37E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373426BB-35B5-4FE3-8EA6-3EBF0BC0B61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
   <si>
     <t>Sprint</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t xml:space="preserve">Read load cell values with HX711 module using a known weight </t>
+  </si>
+  <si>
+    <t>Read temp and humidity values from DHT22 sensor</t>
   </si>
 </sst>
 </file>
@@ -551,7 +554,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1009"/>
+  <dimension ref="A1:Z1010"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -974,7 +977,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -985,7 +988,7 @@
         <v>61</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>10</v>
@@ -997,25 +1000,21 @@
         <v>3</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>62</v>
+      </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16" s="3">
         <v>3</v>
@@ -1027,50 +1026,52 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="3">
-        <v>7</v>
-      </c>
-      <c r="H17" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
       <c r="I17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
@@ -1079,40 +1080,53 @@
     </row>
     <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B19" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+    <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="3">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="3">
+        <v>7</v>
+      </c>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
@@ -1136,6 +1150,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
@@ -1147,9 +1162,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -1169,6 +1184,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
@@ -1219,7 +1235,6 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
@@ -1230,6 +1245,7 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
@@ -1240,7 +1256,6 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
@@ -1264,20 +1279,20 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+    <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1288,6 +1303,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
@@ -1318,7 +1334,6 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
@@ -1329,6 +1344,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -1339,7 +1355,6 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
@@ -1350,6 +1365,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
@@ -1361,48 +1377,57 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+    </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="6" t="s">
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="7"/>
-    </row>
-    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C49" s="7"/>
     </row>
     <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C53" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2359,18 +2384,19 @@
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F36:F38 F2:F34" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F37:F39 F2:F35" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I36:I44 I25:I34 I2:I23" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I37:I45 I26:I35 I2:I24" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E36:E44 E16:E34 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E37:E45 E17:E35 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373426BB-35B5-4FE3-8EA6-3EBF0BC0B61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA162C4-903C-4C02-A581-656F56BA9F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="72">
   <si>
     <t>Sprint</t>
   </si>
@@ -227,6 +227,15 @@
   </si>
   <si>
     <t>Read temp and humidity values from DHT22 sensor</t>
+  </si>
+  <si>
+    <t>US19</t>
+  </si>
+  <si>
+    <t>Write the RTOS code for existing firmware</t>
+  </si>
+  <si>
+    <t>Integrating all sensors to main code and ensure they are all working without timing issues .</t>
   </si>
 </sst>
 </file>
@@ -554,7 +563,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1010"/>
+  <dimension ref="A1:Z1012"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -841,8 +850,12 @@
       <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3</v>
+      </c>
       <c r="I9" s="3" t="s">
         <v>11</v>
       </c>
@@ -907,6 +920,9 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -926,7 +942,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -958,6 +974,9 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B14" s="3">
         <v>13</v>
       </c>
@@ -981,6 +1000,9 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
@@ -1004,11 +1026,14 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="B16" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>62</v>
@@ -1031,10 +1056,10 @@
         <v>44</v>
       </c>
       <c r="B17" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>48</v>
@@ -1058,10 +1083,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>50</v>
@@ -1071,86 +1096,118 @@
         <v>12</v>
       </c>
       <c r="G18" s="3">
-        <v>7</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3</v>
+      </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" s="3">
-        <v>5</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4</v>
+      </c>
       <c r="I19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>7</v>
-      </c>
-      <c r="H20" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5</v>
+      </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+    <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="3">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="3">
+        <v>5</v>
+      </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="3">
+        <v>19</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7</v>
+      </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
@@ -1158,10 +1215,17 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="3">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
@@ -1169,83 +1233,117 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="I28" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="I29" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="I30" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
@@ -1277,7 +1375,6 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1290,9 +1387,16 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+    <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1305,15 +1409,9 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+    <row r="38" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3"/>
@@ -1324,6 +1422,7 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
@@ -1344,7 +1443,6 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -1386,50 +1484,69 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-    </row>
-    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+    </row>
     <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="6" t="s">
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="7"/>
-    </row>
-    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="C51" s="7"/>
     </row>
     <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2385,18 +2502,20 @@
     <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F37:F39 F2:F35" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F39:F41 F2:F37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I37:I45 I26:I35 I2:I24" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I39:I47 I2:I37" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E37:E45 E17:E35 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E39:E47 E17:E37 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA162C4-903C-4C02-A581-656F56BA9F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7716595-FA9B-4BF3-9B68-2C114B2910FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="76">
   <si>
     <t>Sprint</t>
   </si>
@@ -236,6 +236,18 @@
   </si>
   <si>
     <t>Integrating all sensors to main code and ensure they are all working without timing issues .</t>
+  </si>
+  <si>
+    <t>US20</t>
+  </si>
+  <si>
+    <t>Rewrite the existing firmware code into RTOS</t>
+  </si>
+  <si>
+    <t>US21</t>
+  </si>
+  <si>
+    <t>US22</t>
   </si>
 </sst>
 </file>
@@ -563,7 +575,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1012"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -1159,73 +1171,82 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" s="3">
         <v>5</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3">
+        <v>5</v>
+      </c>
       <c r="I21" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+    <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="3">
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3">
-        <v>4</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
@@ -1237,7 +1258,9 @@
         <v>10</v>
       </c>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3">
+        <v>4</v>
+      </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
@@ -1257,6 +1280,7 @@
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
@@ -1272,9 +1296,9 @@
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1302,6 +1326,7 @@
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
@@ -1350,10 +1375,14 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
@@ -1364,7 +1393,6 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
@@ -1375,6 +1403,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1385,7 +1414,6 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1409,20 +1437,20 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
@@ -1433,6 +1461,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
@@ -1463,7 +1492,6 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
@@ -1474,6 +1502,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
@@ -1484,7 +1513,6 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
@@ -1495,6 +1523,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
@@ -1506,48 +1535,57 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+    </row>
     <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="7"/>
-    </row>
-    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C52" s="7"/>
     </row>
     <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C56" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2504,18 +2542,19 @@
     <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F39:F41 F2:F37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F40:F42 F2:F38" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I39:I47 I2:I37" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I40:I48 I2:I38" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E39:E47 E17:E37 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E40:E48 E17:E38 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7716595-FA9B-4BF3-9B68-2C114B2910FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5540ED-9DAA-4182-876F-FB6C849FDCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="78">
   <si>
     <t>Sprint</t>
   </si>
@@ -248,6 +248,12 @@
   </si>
   <si>
     <t>US22</t>
+  </si>
+  <si>
+    <t>Debug load cell code since load cell value is not printing every 1 second as per the delay added in the program.</t>
+  </si>
+  <si>
+    <t>US23</t>
   </si>
 </sst>
 </file>
@@ -575,7 +581,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1013"/>
+  <dimension ref="A1:Z1014"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -1118,9 +1124,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="A19" s="2"/>
       <c r="B19" s="3">
         <v>18</v>
       </c>
@@ -1128,20 +1132,20 @@
         <v>66</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1155,17 +1159,17 @@
         <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
@@ -1173,7 +1177,7 @@
     </row>
     <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" s="3">
         <v>20</v>
@@ -1182,7 +1186,7 @@
         <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
@@ -1198,7 +1202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
@@ -1209,23 +1213,25 @@
         <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22" s="3">
         <v>5</v>
       </c>
-      <c r="H22" s="3"/>
+      <c r="H22" s="3">
+        <v>5</v>
+      </c>
       <c r="I22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3">
         <v>22</v>
@@ -1234,37 +1240,44 @@
         <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+    <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3">
-        <v>4</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G24" s="3">
+        <v>7</v>
+      </c>
+      <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
@@ -1296,6 +1309,7 @@
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
@@ -1311,9 +1325,9 @@
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1341,6 +1355,7 @@
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
@@ -1389,10 +1404,14 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="I33" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
@@ -1403,7 +1422,6 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1414,6 +1432,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1424,7 +1443,6 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1448,20 +1466,20 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
@@ -1472,6 +1490,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -1502,7 +1521,6 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
@@ -1513,6 +1531,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
@@ -1523,7 +1542,6 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
@@ -1534,6 +1552,7 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
     </row>
     <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
@@ -1545,55 +1564,64 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+    <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="7"/>
-    </row>
-    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+      <c r="C53" s="7"/>
+    </row>
+    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C54" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
+    <row r="55" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="4" t="s">
+    <row r="56" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C56" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="4" t="s">
+    <row r="57" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C57" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2543,18 +2571,19 @@
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F40:F42 F2:F38" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F41:F43 F2:F39" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I40:I48 I2:I38" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I41:I49 I2:I39" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E40:E48 E17:E38 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E41:E49 E17:E39 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5540ED-9DAA-4182-876F-FB6C849FDCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304E1048-DBF1-401A-8A61-F211859A6944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="79">
   <si>
     <t>Sprint</t>
   </si>
@@ -232,18 +232,12 @@
     <t>US19</t>
   </si>
   <si>
-    <t>Write the RTOS code for existing firmware</t>
-  </si>
-  <si>
     <t>Integrating all sensors to main code and ensure they are all working without timing issues .</t>
   </si>
   <si>
     <t>US20</t>
   </si>
   <si>
-    <t>Rewrite the existing firmware code into RTOS</t>
-  </si>
-  <si>
     <t>US21</t>
   </si>
   <si>
@@ -254,6 +248,15 @@
   </si>
   <si>
     <t>US23</t>
+  </si>
+  <si>
+    <t>Write the RTOS code for existing firmware: Create task for each sensor and implement the IPC mechanism</t>
+  </si>
+  <si>
+    <t>Interface LCD monitor using I2C for displaying output data</t>
+  </si>
+  <si>
+    <t>4-wire load cell need to be procured .Currently the 3 wire load cell is causing drift in reading without any weight.</t>
   </si>
 </sst>
 </file>
@@ -581,7 +584,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1014"/>
+  <dimension ref="A1:Z1015"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -1132,7 +1135,7 @@
         <v>66</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
@@ -1145,7 +1148,7 @@
         <v>2</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1159,17 +1162,17 @@
         <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
@@ -1183,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
@@ -1210,10 +1213,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
@@ -1229,71 +1232,80 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>46</v>
-      </c>
+    <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
       <c r="B23" s="3">
         <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" s="3">
         <v>5</v>
       </c>
-      <c r="H23" s="3"/>
+      <c r="H23" s="3">
+        <v>5</v>
+      </c>
       <c r="I23" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B24" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+    <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="3">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="G25" s="3">
+        <v>7</v>
+      </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
@@ -1325,6 +1337,7 @@
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
@@ -1340,9 +1353,9 @@
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1370,6 +1383,7 @@
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
@@ -1418,10 +1432,14 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="I34" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1432,7 +1450,6 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1443,6 +1460,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1453,7 +1471,6 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
@@ -1477,20 +1494,20 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
+    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -1501,6 +1518,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
@@ -1531,7 +1549,6 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
@@ -1542,6 +1559,7 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
@@ -1552,7 +1570,6 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
     </row>
     <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
@@ -1563,6 +1580,7 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
@@ -1574,48 +1592,57 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+    </row>
     <row r="51" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="7"/>
-    </row>
-    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C54" s="7"/>
     </row>
     <row r="55" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C58" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2572,18 +2599,19 @@
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F41:F43 F2:F39" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F42:F44 F2:F40" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I41:I49 I2:I39" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I42:I50 I2:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E41:E49 E17:E39 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E42:E50 E17:E40 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304E1048-DBF1-401A-8A61-F211859A6944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3820F1A6-B244-4290-A553-5DE08486E61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
   <si>
     <t>Sprint</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>4-wire load cell need to be procured .Currently the 3 wire load cell is causing drift in reading without any weight.</t>
+  </si>
+  <si>
+    <t>US24</t>
   </si>
 </sst>
 </file>
@@ -1172,10 +1175,10 @@
         <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1199,10 +1202,10 @@
         <v>5</v>
       </c>
       <c r="H21" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1262,10 +1265,10 @@
         <v>46</v>
       </c>
       <c r="B24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>52</v>
@@ -1277,9 +1280,11 @@
       <c r="G24" s="3">
         <v>5</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="3">
+        <v>4</v>
+      </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1287,10 +1292,10 @@
         <v>53</v>
       </c>
       <c r="B25" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>55</v>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3820F1A6-B244-4290-A553-5DE08486E61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613BA6CD-0324-4CD1-8DC9-BBA52AD7E7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
   <si>
     <t>Sprint</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>US24</t>
+  </si>
+  <si>
+    <t>US25</t>
+  </si>
+  <si>
+    <t>Write a code in python to plot the concentration of gases</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1078,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1099,7 +1105,7 @@
         <v>3</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1307,22 +1313,34 @@
       <c r="G25" s="3">
         <v>7</v>
       </c>
-      <c r="H25" s="3"/>
+      <c r="H25" s="3">
+        <v>7</v>
+      </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="B26" s="3">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="G26" s="3">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>3</v>
+      </c>
       <c r="I26" s="3" t="s">
         <v>13</v>
       </c>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613BA6CD-0324-4CD1-8DC9-BBA52AD7E7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C80C52-6C0A-45A1-90D2-24520DBB5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="82">
   <si>
     <t>Sprint</t>
   </si>
@@ -1136,7 +1136,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="B19" s="3">
         <v>18</v>
       </c>
@@ -1162,7 +1164,7 @@
     </row>
     <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="3">
         <v>19</v>
@@ -1184,12 +1186,12 @@
         <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B21" s="3">
         <v>20</v>
@@ -1242,7 +1244,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="B23" s="3">
         <v>22</v>
       </c>
@@ -1268,7 +1272,7 @@
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3">
         <v>23</v>
@@ -1321,7 +1325,9 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="B26" s="3">
         <v>25</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J26" s="3"/>
     </row>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C80C52-6C0A-45A1-90D2-24520DBB5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B462E229-0C88-4E33-B710-B198AD103B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
   <si>
     <t>Sprint</t>
   </si>
@@ -241,9 +241,6 @@
     <t>US21</t>
   </si>
   <si>
-    <t>US22</t>
-  </si>
-  <si>
     <t>Debug load cell code since load cell value is not printing every 1 second as per the delay added in the program.</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
   </si>
   <si>
     <t>Interface LCD monitor using I2C for displaying output data</t>
-  </si>
-  <si>
-    <t>4-wire load cell need to be procured .Currently the 3 wire load cell is causing drift in reading without any weight.</t>
   </si>
   <si>
     <t>US24</t>
@@ -999,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L13" s="2"/>
     </row>
@@ -1132,7 +1126,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1146,7 +1140,7 @@
         <v>66</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
@@ -1173,7 +1167,7 @@
         <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
@@ -1213,7 +1207,7 @@
         <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1227,7 +1221,7 @@
         <v>72</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
@@ -1248,13 +1242,13 @@
         <v>53</v>
       </c>
       <c r="B23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
@@ -1264,10 +1258,10 @@
         <v>5</v>
       </c>
       <c r="H23" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1275,23 +1269,23 @@
         <v>53</v>
       </c>
       <c r="B24" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>15</v>
@@ -1302,54 +1296,30 @@
         <v>53</v>
       </c>
       <c r="B25" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H25" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="3">
-        <v>25</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3">
-        <v>3</v>
-      </c>
-      <c r="H26" s="3">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A26" s="2"/>
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,13 +2604,13 @@
     <mergeCell ref="B54:C54"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F42:F44 F2:F40" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F42:F44 F2:F25 F27:F40" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I42:I50 I2:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I42:I50 I2:I25 I27:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E42:E50 E17:E40 E13 E2:E11" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E42:E50 E13 E2:E11 E17:E25 E27:E40" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$L$10:$L$14</formula1>
     </dataValidation>
   </dataValidations>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B462E229-0C88-4E33-B710-B198AD103B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CDC274-1B0D-4836-B90F-E7DC8F494D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1234,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CDC274-1B0D-4836-B90F-E7DC8F494D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6185EBF-DC59-4D8D-A318-F6FACBAD5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="83">
   <si>
     <t>Sprint</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Selection and evaluation of LPG gas sensor based on sensitivity and response time</t>
   </si>
   <si>
-    <t>Evaluate the power requirement for entire system and select suitable voltage source.Estimate voltage and current requirement for stable operation.</t>
-  </si>
-  <si>
     <t>Sprint 4</t>
   </si>
   <si>
@@ -260,6 +257,18 @@
   </si>
   <si>
     <t>Write a code in python to plot the concentration of gases</t>
+  </si>
+  <si>
+    <t>US22</t>
+  </si>
+  <si>
+    <t>Add a buzzer to alert the user on occurance of potential gas leakage</t>
+  </si>
+  <si>
+    <t>Add GSM module to communicate leak status to registered user on occurance of potential risk</t>
+  </si>
+  <si>
+    <t>Sprint 7</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1015"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -778,7 +787,7 @@
     </row>
     <row r="6" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -787,23 +796,23 @@
         <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -814,25 +823,25 @@
         <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
+      <c r="G7" s="3">
+        <v>3</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3">
         <v>7</v>
@@ -841,7 +850,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
@@ -855,6 +864,9 @@
       </c>
       <c r="I8" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -868,7 +880,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
@@ -883,9 +895,7 @@
       <c r="I9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
@@ -895,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
@@ -915,7 +925,7 @@
       </c>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
@@ -923,12 +933,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>58</v>
+      </c>
       <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
@@ -941,9 +950,8 @@
       <c r="I11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -951,11 +959,12 @@
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
@@ -968,8 +977,9 @@
       <c r="I12" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -977,12 +987,11 @@
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>59</v>
+      </c>
       <c r="F13" s="3" t="s">
         <v>10</v>
       </c>
@@ -995,7 +1004,6 @@
       <c r="I13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -1005,10 +1013,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -1025,16 +1033,16 @@
     </row>
     <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B15" s="3">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>10</v>
@@ -1049,21 +1057,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="3">
         <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3">
         <v>3</v>
@@ -1075,18 +1084,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="3">
         <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
@@ -1104,26 +1113,26 @@
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3">
         <v>17</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>11</v>
@@ -1131,26 +1140,26 @@
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="3">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>11</v>
@@ -1158,16 +1167,16 @@
     </row>
     <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3">
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
@@ -1185,16 +1194,16 @@
     </row>
     <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="3">
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
@@ -1204,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>11</v>
@@ -1212,16 +1221,16 @@
     </row>
     <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3">
         <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
@@ -1231,34 +1240,34 @@
         <v>5</v>
       </c>
       <c r="H22" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>15</v>
@@ -1266,61 +1275,85 @@
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H24" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="J26" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3">
+        <v>4</v>
+      </c>
+      <c r="H26" s="3">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
@@ -1339,7 +1372,6 @@
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -1352,9 +1384,9 @@
       <c r="I28" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1367,7 +1399,6 @@
       <c r="I29" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
@@ -1382,7 +1413,6 @@
       <c r="I30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
@@ -1417,28 +1447,21 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1470,6 +1493,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3"/>
@@ -1482,16 +1506,9 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+    <row r="39" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
@@ -1504,9 +1521,15 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
     </row>
     <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
@@ -1517,7 +1540,6 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
@@ -1538,6 +1560,7 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
@@ -1579,75 +1602,56 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-    </row>
-    <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="6" t="s">
+    </row>
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="7"/>
-    </row>
-    <row r="55" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="7"/>
+    </row>
+    <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2597,21 +2601,19 @@
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1014" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1015" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B52:C52"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F42:F44 F2:F25 F27:F40" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F40:F42 F25:F38 F2:F24" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$L$3:$L$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I42:I50 I2:I25 I27:I40" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I40:I48 I25:I38 I2:I24" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$3:$N$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E42:E50 E13 E2:E11 E17:E25 E27:E40" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$L$10:$L$14</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E40:E48 E25:E38 E16:E24 E2:E10 E12" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>$L$9:$L$13</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6185EBF-DC59-4D8D-A318-F6FACBAD5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3535764F-F98C-4906-85FF-FBF593AFA58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1243,7 +1243,7 @@
         <v>4</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1270,7 +1270,7 @@
         <v>7</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1324,7 +1324,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J25" s="3"/>
     </row>
@@ -1352,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3535764F-F98C-4906-85FF-FBF593AFA58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5770D1C1-A35D-4209-AE3C-43720E89DB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1352,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Documents/Safeflame_Product Backlog_Rithika.xlsx
+++ b/Documents/Safeflame_Product Backlog_Rithika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\SafeFlame\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5770D1C1-A35D-4209-AE3C-43720E89DB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB645BDA-AD28-4EB5-B5A0-A6D6D17F4653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="79">
   <si>
     <t>Sprint</t>
   </si>
@@ -64,12 +64,6 @@
     <t>To Do</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Abbreviations</t>
   </si>
   <si>
@@ -109,13 +103,7 @@
     <t>Identifying load cell for monitoring the weight of the gas cylinder.The load cell should be able to identify gas change as small as 100g.</t>
   </si>
   <si>
-    <t xml:space="preserve">Conduct a feasibility check for including an automatic shut-off valve in case of occurance high risk gas leak </t>
-  </si>
-  <si>
     <t>US2</t>
-  </si>
-  <si>
-    <t>US3</t>
   </si>
   <si>
     <t>Sprint 2</t>
@@ -596,7 +584,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1013"/>
+  <dimension ref="A1:Z1012"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -660,16 +648,16 @@
     </row>
     <row r="2" spans="1:26" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3" t="s">
@@ -688,16 +676,16 @@
     </row>
     <row r="3" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3" t="s">
@@ -719,51 +707,51 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
@@ -778,52 +766,46 @@
       <c r="I5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="3">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
@@ -838,19 +820,22 @@
       <c r="I7" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="L7" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
@@ -865,22 +850,20 @@
       <c r="I8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
@@ -897,20 +880,19 @@
       </c>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>54</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>10</v>
       </c>
@@ -923,21 +905,21 @@
       <c r="I10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
         <v>10</v>
       </c>
@@ -950,21 +932,21 @@
       <c r="I11" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>55</v>
+      </c>
       <c r="F12" s="3" t="s">
         <v>10</v>
       </c>
@@ -977,20 +959,19 @@
       <c r="I12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>10</v>
@@ -1007,16 +988,16 @@
     </row>
     <row r="14" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>10</v>
@@ -1031,21 +1012,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="3">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15" s="3">
         <v>3</v>
@@ -1057,18 +1039,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B16" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
@@ -1086,26 +1068,26 @@
     </row>
     <row r="17" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>11</v>
@@ -1113,26 +1095,26 @@
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B18" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>11</v>
@@ -1140,16 +1122,16 @@
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
@@ -1167,16 +1149,16 @@
     </row>
     <row r="20" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
@@ -1186,7 +1168,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>11</v>
@@ -1194,16 +1176,16 @@
     </row>
     <row r="21" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
@@ -1213,34 +1195,34 @@
         <v>5</v>
       </c>
       <c r="H21" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>11</v>
@@ -1248,127 +1230,107 @@
     </row>
     <row r="23" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H23" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B24" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="3">
-        <v>25</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>81</v>
-      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3">
-        <v>4</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1376,71 +1338,50 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
@@ -1451,6 +1392,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
@@ -1461,7 +1403,6 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
@@ -1472,6 +1413,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3"/>
@@ -1495,20 +1437,20 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="39" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+    <row r="38" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
@@ -1519,7 +1461,6 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
@@ -1550,6 +1491,7 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
@@ -1560,7 +1502,6 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3"/>
@@ -1571,6 +1512,7 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3"/>
@@ -1581,7 +1523,6 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
     </row>
     <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
@@ -1593,24 +1534,22 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-    </row>
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="7"/>
+    </row>
     <row r="52" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="7"/>
     </row>
     <row r="53" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
@@ -1636,14 +1575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2600,20 +2532,19 @@
     <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F40:F42 F25:F38 F2:F24" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$L$3:$L$5</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F39:F41 F2:F37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>$L$3:$L$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I40:I48 I25:I38 I2:I24" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>$N$3:$N$5</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I39:I47 I2:I37" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>$N$3:$N$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E40:E48 E25:E38 E16:E24 E2:E10 E12" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$L$9:$L$13</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E39:E47 E11 E2:E9 E15:E37" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>$L$8:$L$12</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
